--- a/data/trans_camb/LAWTONB_2R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 5,67</t>
+          <t>-15,81; 6,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 1,02</t>
+          <t>-18,82; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 13,62</t>
+          <t>-5,45; 15,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 16,36</t>
+          <t>-4,66; 16,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 15,37</t>
+          <t>-6,21; 15,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 25,02</t>
+          <t>6,09; 24,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 9,1</t>
+          <t>-6,39; 9,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 5,1</t>
+          <t>-8,56; 5,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 17,71</t>
+          <t>3,93; 16,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 21,0</t>
+          <t>-45,85; 25,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,53; 5,98</t>
+          <t>-55,83; 5,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 57,8</t>
+          <t>-16,28; 65,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 63,69</t>
+          <t>-13,68; 65,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 63,3</t>
+          <t>-18,01; 60,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,42; 105,49</t>
+          <t>15,75; 102,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 35,2</t>
+          <t>-18,51; 35,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 20,46</t>
+          <t>-26,29; 23,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 69,57</t>
+          <t>11,3; 66,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 8,19</t>
+          <t>-14,39; 7,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 2,07</t>
+          <t>-18,42; 2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 2,18</t>
+          <t>-16,2; 2,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 19,73</t>
+          <t>-2,13; 20,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 9,06</t>
+          <t>-11,2; 10,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 13,12</t>
+          <t>-4,63; 12,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 11,17</t>
+          <t>-3,67; 11,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 3,15</t>
+          <t>-10,94; 4,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,69</t>
+          <t>-7,19; 5,67</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 29,47</t>
+          <t>-38,23; 29,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 7,32</t>
+          <t>-47,27; 8,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 8,06</t>
+          <t>-41,07; 9,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 60,7</t>
+          <t>-5,45; 64,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 29,47</t>
+          <t>-27,08; 32,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 42,1</t>
+          <t>-10,64; 38,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 35,43</t>
+          <t>-9,27; 37,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 10,31</t>
+          <t>-28,1; 13,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 17,79</t>
+          <t>-17,98; 18,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 18,17</t>
+          <t>-6,21; 19,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 12,47</t>
+          <t>-8,42; 13,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 9,05</t>
+          <t>-12,04; 8,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 16,17</t>
+          <t>-9,05; 14,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 15,59</t>
+          <t>-8,82; 15,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 6,92</t>
+          <t>-37,57; 7,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 13,2</t>
+          <t>-4,82; 13,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 11,25</t>
+          <t>-5,79; 11,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 4,61</t>
+          <t>-25,43; 5,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 128,65</t>
+          <t>-24,45; 123,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 77,4</t>
+          <t>-32,42; 92,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 67,68</t>
+          <t>-42,27; 54,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 59,18</t>
+          <t>-22,68; 53,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 53,38</t>
+          <t>-22,29; 54,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 22,81</t>
+          <t>-88,44; 27,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 54,98</t>
+          <t>-14,66; 54,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 47,1</t>
+          <t>-17,44; 50,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,59; 17,53</t>
+          <t>-74,88; 18,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 15,48</t>
+          <t>-4,6; 15,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 4,12</t>
+          <t>-12,4; 4,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 8,42</t>
+          <t>-7,7; 8,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,0</t>
+          <t>-11,04; 8,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 9,14</t>
+          <t>-9,39; 9,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 11,86</t>
+          <t>-3,78; 11,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 8,55</t>
+          <t>-5,2; 8,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 4,52</t>
+          <t>-8,62; 4,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,7</t>
+          <t>-3,34; 7,94</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 88,43</t>
+          <t>-17,32; 95,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 23,57</t>
+          <t>-46,79; 30,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 55,58</t>
+          <t>-29,97; 55,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 27,88</t>
+          <t>-28,4; 28,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 29,69</t>
+          <t>-24,58; 33,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 40,67</t>
+          <t>-9,64; 40,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 32,85</t>
+          <t>-15,67; 35,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 17,43</t>
+          <t>-27,21; 18,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 31,4</t>
+          <t>-10,13; 31,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,5</t>
+          <t>-5,02; 5,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,37</t>
+          <t>-10,56; -0,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 3,8</t>
+          <t>-5,88; 3,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,08</t>
+          <t>-1,09; 9,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 6,19</t>
+          <t>-3,92; 6,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 8,45</t>
+          <t>-17,04; 8,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,43</t>
+          <t>-1,55; 6,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,3</t>
+          <t>-5,32; 1,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 4,48</t>
+          <t>-11,76; 4,64</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 27,87</t>
+          <t>-17,45; 23,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,16; -1,34</t>
+          <t>-35,8; -1,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 16,93</t>
+          <t>-20,14; 16,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 31,6</t>
+          <t>-2,88; 29,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 19,51</t>
+          <t>-10,46; 22,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 25,93</t>
+          <t>-48,21; 25,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 22,39</t>
+          <t>-4,77; 21,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 7,81</t>
+          <t>-16,09; 6,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 14,71</t>
+          <t>-35,96; 15,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,04</t>
+          <t>15,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,86</t>
+          <t>10,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 6,15</t>
+          <t>-15,82; 6,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 1,43</t>
+          <t>-19,57; 1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 15,04</t>
+          <t>-7,33; 13,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 16,26</t>
+          <t>-3,13; 17,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 15,38</t>
+          <t>-7,27; 13,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 24,18</t>
+          <t>6,92; 24,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 9,18</t>
+          <t>-7,05; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 5,87</t>
+          <t>-9,58; 5,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 16,95</t>
+          <t>3,42; 16,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 25,53</t>
+          <t>-45,03; 29,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,83; 5,86</t>
+          <t>-54,62; 5,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 65,95</t>
+          <t>-20,15; 59,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 65,51</t>
+          <t>-9,5; 69,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 60,29</t>
+          <t>-19,76; 54,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,75; 102,28</t>
+          <t>19,32; 107,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 35,92</t>
+          <t>-20,53; 34,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 23,55</t>
+          <t>-28,41; 20,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 66,59</t>
+          <t>9,92; 65,09</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-7,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 7,93</t>
+          <t>-14,65; 7,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 2,09</t>
+          <t>-17,46; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 2,27</t>
+          <t>-16,47; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 20,63</t>
+          <t>-0,87; 19,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 10,01</t>
+          <t>-10,88; 9,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 12,34</t>
+          <t>-4,78; 12,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 11,66</t>
+          <t>-3,61; 11,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,3</t>
+          <t>-11,35; 3,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,67</t>
+          <t>-6,42; 5,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,8%</t>
+          <t>-23,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,0%</t>
+          <t>-2,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 29,09</t>
+          <t>-38,98; 25,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 8,34</t>
+          <t>-44,98; 7,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 9,75</t>
+          <t>-43,54; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 64,44</t>
+          <t>-1,96; 63,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 32,53</t>
+          <t>-25,92; 27,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 38,76</t>
+          <t>-10,91; 41,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 37,28</t>
+          <t>-9,64; 37,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 13,92</t>
+          <t>-29,21; 12,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 18,06</t>
+          <t>-16,38; 17,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,25</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,42</t>
+          <t>1,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 19,07</t>
+          <t>-5,74; 18,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 13,38</t>
+          <t>-9,3; 13,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 8,11</t>
+          <t>-11,47; 8,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 14,91</t>
+          <t>-9,23; 14,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 15,54</t>
+          <t>-8,75; 15,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,57; 7,79</t>
+          <t>-5,31; 14,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 13,26</t>
+          <t>-4,62; 13,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 11,67</t>
+          <t>-5,94; 11,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 5,0</t>
+          <t>-6,03; 8,97</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>-1,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,42%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-36,79%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 123,89</t>
+          <t>-24,27; 119,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 92,37</t>
+          <t>-35,17; 91,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 54,64</t>
+          <t>-40,53; 60,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 53,32</t>
+          <t>-22,49; 52,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 54,62</t>
+          <t>-22,91; 57,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-88,44; 27,73</t>
+          <t>-12,76; 53,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 54,01</t>
+          <t>-13,76; 56,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 50,65</t>
+          <t>-18,24; 49,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-74,88; 18,98</t>
+          <t>-18,22; 38,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 15,3</t>
+          <t>-5,45; 14,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 4,42</t>
+          <t>-13,36; 4,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 8,66</t>
+          <t>-7,36; 7,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 8,29</t>
+          <t>-10,82; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 9,87</t>
+          <t>-9,34; 8,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 11,85</t>
+          <t>-3,67; 12,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 8,68</t>
+          <t>-5,05; 8,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 4,63</t>
+          <t>-8,91; 4,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,94</t>
+          <t>-3,92; 8,02</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 95,08</t>
+          <t>-21,38; 86,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 30,3</t>
+          <t>-51,51; 26,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 55,28</t>
+          <t>-28,94; 46,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,4; 28,41</t>
+          <t>-26,88; 27,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 33,59</t>
+          <t>-24,01; 30,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 40,49</t>
+          <t>-9,57; 43,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 35,76</t>
+          <t>-15,63; 33,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 18,36</t>
+          <t>-27,11; 17,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 31,65</t>
+          <t>-11,52; 32,2</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>3,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,44</t>
+          <t>-5,03; 5,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -0,32</t>
+          <t>-10,62; -0,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,79</t>
+          <t>-6,64; 3,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,36</t>
+          <t>-1,06; 9,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,94</t>
+          <t>-4,02; 6,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 8,69</t>
+          <t>2,34; 11,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,28</t>
+          <t>-1,7; 6,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,86</t>
+          <t>-5,41; 1,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,64</t>
+          <t>-0,16; 6,63</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,86%</t>
+          <t>-6,11%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,68%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-2,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 23,0</t>
+          <t>-17,24; 26,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -1,19</t>
+          <t>-35,6; -3,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 16,09</t>
+          <t>-22,15; 13,63</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 29,22</t>
+          <t>-3,13; 30,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 22,27</t>
+          <t>-11,17; 21,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 25,9</t>
+          <t>6,22; 37,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,2</t>
+          <t>-4,96; 20,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 6,43</t>
+          <t>-16,63; 6,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 15,48</t>
+          <t>-0,43; 23,27</t>
         </is>
       </c>
     </row>
